--- a/config/yunying/passport_recharge.xlsx
+++ b/config/yunying/passport_recharge.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="passport_recharge" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="passport_recharge" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1152,12 +1152,6 @@
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1173,8 +1167,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>""</t>
@@ -1311,7 +1303,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>マスターパス</t>
+          <t>主路径</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1349,9 +1341,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>activity/passport/tips/kaitong.png</t>
@@ -1359,7 +1348,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>#C0x5b545b#マスターパスが#C0x72c1a1#解放 \n#C0xf76b45#専属任務#C0x5b545b#が受取可能</t>
+          <t>#C0x5b545b#主卡#C0x72c1a1#解放\n#C0xf76b45#专属任务#C0x5b545b#可领取</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1396,7 +1385,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>高級マスターパス</t>
+          <t>豪华主通行证</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1434,7 +1423,6 @@
           <t>50</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>2</t>
@@ -1452,7 +1440,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>#C0x5b545b#専属任務が受取可能 \nパスレベルが即#C0xf76b45#50#C0x5b545b#上昇</t>
+          <t>#C0x5b545b#专属任务可领取\n路径等级立即提升#C0xf76b45#50#C0x5b545b#</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1482,25 +1470,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" s="1" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1510,7 +1481,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>300パス経験値</t>
+          <t>300传球经验值</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1543,21 +1514,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1567,7 +1529,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>1000パス経験値</t>
+          <t>1000传球经验值</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1600,21 +1562,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1624,7 +1577,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>2200パス経験値</t>
+          <t>2200传球经验值</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1657,21 +1610,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>2200</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1681,7 +1625,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>8000パス経験値</t>
+          <t>8000传球经验值</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1714,21 +1658,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>8000</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
